--- a/data/trans_dic/IP16A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 36,65</t>
+          <t>4,49; 35,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,54</t>
+          <t>0,0; 14,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,56</t>
+          <t>0,0; 19,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,92</t>
+          <t>0,0; 26,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,04</t>
+          <t>0,0; 30,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 32,17</t>
+          <t>3,07; 30,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 15,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 23,7</t>
+          <t>2,45; 24,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,21</t>
+          <t>0,0; 17,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 19,27</t>
+          <t>2,13; 18,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,92</t>
+          <t>0,0; 19,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,81</t>
+          <t>0,0; 21,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,47</t>
+          <t>0,0; 18,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 15,22</t>
+          <t>1,79; 15,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,03</t>
+          <t>0,0; 10,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,87</t>
+          <t>0,0; 36,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,21</t>
+          <t>0,0; 24,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,97</t>
+          <t>0,0; 26,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,85</t>
+          <t>0,0; 24,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 24,32</t>
+          <t>2,82; 24,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 9,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,25</t>
+          <t>0,0; 12,31</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,6</t>
+          <t>0,0; 19,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,15</t>
+          <t>0,0; 13,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,23</t>
+          <t>0,0; 23,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,2</t>
+          <t>0,0; 13,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 6,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,36</t>
+          <t>0,0; 22,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,11</t>
+          <t>0,0; 29,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,92</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,23</t>
+          <t>0,0; 19,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 37,99</t>
+          <t>4,93; 39,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,43</t>
+          <t>0,0; 35,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,63</t>
+          <t>0,0; 34,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,57</t>
+          <t>0,0; 16,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 30,0</t>
+          <t>5,39; 27,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,41</t>
+          <t>0,0; 17,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 29,62</t>
+          <t>7,27; 29,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 26,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 19,39</t>
+          <t>1,41; 19,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 26,11</t>
+          <t>5,15; 26,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 18,64</t>
+          <t>2,47; 20,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,97</t>
+          <t>0,0; 36,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 19,25</t>
+          <t>3,42; 20,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 14,76</t>
+          <t>2,88; 15,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 19,92</t>
+          <t>6,22; 21,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 20,56</t>
+          <t>2,36; 20,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,27</t>
+          <t>3,75; 16,1</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,28</t>
+          <t>0,0; 14,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,26</t>
+          <t>0,0; 14,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 12,84</t>
+          <t>1,49; 13,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 23,97</t>
+          <t>2,7; 22,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,65</t>
+          <t>1,85; 10,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 16,05</t>
+          <t>2,94; 16,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,78</t>
+          <t>2,94; 9,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,02</t>
+          <t>2,24; 7,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,36</t>
+          <t>0,55; 4,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,48</t>
+          <t>0,44; 4,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,22</t>
+          <t>4,23; 11,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,26</t>
+          <t>1,7; 7,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,31</t>
+          <t>2,48; 9,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,31</t>
+          <t>1,62; 6,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,37</t>
+          <t>4,5; 9,23</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,28</t>
+          <t>2,53; 6,3</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,68</t>
+          <t>1,95; 5,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,52</t>
+          <t>1,35; 4,09</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1693</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1226</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2501</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1725</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>523; 4086</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2286</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3101</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3274</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5561</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>589; 5859</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3534</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>584; 5759</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5867</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>751; 6623</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3749</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2169</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4290</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4710</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>656; 5823</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5049</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4276</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3865</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4726</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2553</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>626; 5395</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3642</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4707</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2539</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3858</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4350</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2388</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2823</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3124</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2765</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3626</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1197</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>610; 4850</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3944</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3654</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3031</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1245; 6373</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5106</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4146</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4047</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1931; 7817</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3720</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>419; 5739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1367; 6967</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>625; 5313</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3848</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1518; 9193</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1384; 7597</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>3227; 10935</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>587; 5210</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2777; 11936</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3063</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3579</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3716</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3053</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>594; 5272</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>676; 5618</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1217; 6853</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>1353; 7347</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>6081</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>17740</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>3687; 12295</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3304; 11738</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>696; 5671</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>773; 7380</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>6085; 16642</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2685; 12296</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3055; 11275</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2957; 11929</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>12127; 24861</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>7727; 19215</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>4879; 14984</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>4848; 14734</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 35,02</t>
+          <t>4,57; 39,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,64</t>
+          <t>0,0; 14,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,27</t>
+          <t>0,0; 23,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,98</t>
+          <t>0,0; 33,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,85</t>
+          <t>0,0; 26,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 30,51</t>
+          <t>3,2; 29,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,83</t>
+          <t>0,0; 15,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 24,19</t>
+          <t>2,41; 24,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,44</t>
+          <t>0,0; 18,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 18,76</t>
+          <t>2,33; 20,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,63</t>
+          <t>0,0; 20,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,6</t>
+          <t>0,0; 23,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,86</t>
+          <t>0,0; 19,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,92</t>
+          <t>1,74; 15,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,42</t>
+          <t>0,0; 12,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,78</t>
+          <t>0,0; 36,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,89</t>
+          <t>0,0; 23,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,34</t>
+          <t>0,0; 25,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,17</t>
+          <t>0,0; 29,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 24,32</t>
+          <t>2,78; 24,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,62</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,31</t>
+          <t>0,0; 12,54</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,06</t>
+          <t>0,0; 16,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,14</t>
+          <t>0,0; 12,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,49</t>
+          <t>0,0; 24,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,27</t>
+          <t>0,0; 13,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,98</t>
+          <t>0,0; 28,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,23</t>
+          <t>0,0; 29,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 10,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,16</t>
+          <t>0,0; 18,72</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,93; 39,18</t>
+          <t>4,95; 41,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,9</t>
+          <t>0,0; 30,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,06</t>
+          <t>0,0; 33,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,75</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 27,58</t>
+          <t>5,29; 28,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,56</t>
+          <t>0,0; 15,97</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 29,43</t>
+          <t>5,41; 28,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,11</t>
+          <t>0,0; 23,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 19,27</t>
+          <t>1,38; 16,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 26,26</t>
+          <t>5,17; 26,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 20,96</t>
+          <t>2,43; 19,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,29</t>
+          <t>0,0; 34,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 20,73</t>
+          <t>2,9; 20,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 15,82</t>
+          <t>2,86; 15,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 21,07</t>
+          <t>5,37; 20,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 20,96</t>
+          <t>2,31; 20,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 16,1</t>
+          <t>3,8; 16,4</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,33</t>
+          <t>0,0; 13,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,59</t>
+          <t>0,0; 15,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,22</t>
+          <t>1,51; 13,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 22,46</t>
+          <t>2,9; 24,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,42</t>
+          <t>1,63; 9,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,0</t>
+          <t>2,94; 15,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,81</t>
+          <t>3,23; 9,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,97</t>
+          <t>2,36; 7,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,45</t>
+          <t>0,54; 4,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,15</t>
+          <t>0,46; 4,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,56</t>
+          <t>4,39; 11,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,78</t>
+          <t>1,85; 7,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,15</t>
+          <t>2,6; 9,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,55</t>
+          <t>1,64; 6,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 9,23</t>
+          <t>4,38; 9,3</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,3</t>
+          <t>2,38; 6,3</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,98</t>
+          <t>1,89; 5,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,09</t>
+          <t>1,32; 4,36</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>523; 4086</t>
+          <t>533; 4600</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2286</t>
+          <t>0; 2253</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3101</t>
+          <t>0; 3719</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3274</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5561</t>
+          <t>0; 4782</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>589; 5859</t>
+          <t>615; 5709</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3534</t>
+          <t>0; 3416</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>584; 5759</t>
+          <t>575; 5944</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5867</t>
+          <t>0; 6221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751; 6623</t>
+          <t>823; 7397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3749</t>
+          <t>0; 3805</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3284</t>
+          <t>0; 3437</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 4616</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4710</t>
+          <t>0; 4824</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>656; 5823</t>
+          <t>637; 5620</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5049</t>
+          <t>0; 5866</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4276</t>
+          <t>0; 4260</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>0; 3671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4726</t>
+          <t>0; 4583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2553</t>
+          <t>0; 3159</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>626; 5395</t>
+          <t>617; 5417</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3642</t>
+          <t>0; 3512</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4707</t>
+          <t>0; 4792</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3116</t>
+          <t>0; 2769</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2539</t>
+          <t>0; 2337</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3858</t>
+          <t>0; 3987</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4350</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2388</t>
+          <t>0; 2361</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2823</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3124</t>
+          <t>0; 3200</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2765</t>
+          <t>0; 2770</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3626</t>
+          <t>0; 3543</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>610; 4850</t>
+          <t>613; 5120</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 3348</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3654</t>
+          <t>0; 3615</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3031</t>
+          <t>0; 3653</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1245; 6373</t>
+          <t>1223; 6498</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5106</t>
+          <t>0; 4644</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3462,57 +3462,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1931; 7817</t>
+          <t>1436; 7637</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3720</t>
+          <t>0; 3309</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>419; 5739</t>
+          <t>411; 5039</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1367; 6967</t>
+          <t>1370; 6984</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>625; 5313</t>
+          <t>616; 4826</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3848</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1518; 9193</t>
+          <t>1287; 9071</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1384; 7597</t>
+          <t>1373; 7656</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3227; 10935</t>
+          <t>2787; 10759</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>587; 5210</t>
+          <t>575; 5207</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2777; 11936</t>
+          <t>2817; 12157</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3716</t>
+          <t>0; 3461</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3053</t>
+          <t>0; 3243</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>594; 5272</t>
+          <t>602; 5383</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>676; 5618</t>
+          <t>726; 6061</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1217; 6853</t>
+          <t>1074; 6504</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1353; 7347</t>
+          <t>1349; 6888</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3687; 12295</t>
+          <t>4042; 12371</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3304; 11738</t>
+          <t>3480; 11430</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>696; 5671</t>
+          <t>693; 5733</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>773; 7380</t>
+          <t>818; 7824</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6085; 16642</t>
+          <t>6322; 17167</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2685; 12296</t>
+          <t>2916; 11872</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3055; 11275</t>
+          <t>3205; 11629</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2957; 11929</t>
+          <t>2987; 11528</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12127; 24861</t>
+          <t>11788; 25026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7727; 19215</t>
+          <t>7275; 19237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4879; 14984</t>
+          <t>4736; 14087</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4848; 14734</t>
+          <t>4735; 15681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>14,51%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,75%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 39,43</t>
+          <t>0,0; 37,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,43</t>
+          <t>0,0; 31,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,11</t>
+          <t>3,04; 32,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,32</t>
+          <t>4,46; 36,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,53</t>
+          <t>0,0; 14,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 29,72</t>
+          <t>0,0; 23,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 24,97</t>
+          <t>3,39; 23,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,5</t>
+          <t>0,0; 16,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 20,96</t>
+          <t>2,36; 19,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
     </row>
@@ -789,32 +789,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,54</t>
+          <t>0,0; 24,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,25</t>
+          <t>0,0; 21,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,36</t>
+          <t>1,75; 15,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,1</t>
+          <t>0,0; 10,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -929,34 +929,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,64</t>
+          <t>0,0; 29,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,91</t>
+          <t>0,0; 36,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 25,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 24,41</t>
+          <t>2,92; 24,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 9,25</t>
         </is>
       </c>
     </row>
@@ -1069,32 +1069,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,93</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,27</t>
+          <t>0,0; 16,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 13,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 12,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,72</t>
+          <t>0,0; 17,09</t>
         </is>
       </c>
     </row>
@@ -1349,32 +1349,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15,64%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,8%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,95; 41,36</t>
+          <t>0,0; 33,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,47</t>
+          <t>0,0; 20,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,69</t>
+          <t>4,89; 37,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,19</t>
+          <t>0,0; 33,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 28,12</t>
+          <t>5,19; 30,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,97</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>15,61%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4,95%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,16; 26,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 28,76</t>
+          <t>2,45; 18,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,22</t>
+          <t>0,0; 35,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 16,92</t>
+          <t>2,69; 18,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 26,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 19,04</t>
+          <t>5,35; 29,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,52</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 20,45</t>
+          <t>1,3; 19,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,94</t>
+          <t>2,79; 14,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 20,73</t>
+          <t>5,31; 19,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 20,95</t>
+          <t>2,41; 20,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,4</t>
+          <t>3,28; 14,17</t>
         </is>
       </c>
     </row>
@@ -1629,37 +1629,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>4,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>4,35%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,35</t>
+          <t>1,5; 12,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,5</t>
+          <t>2,8; 23,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,5</t>
+          <t>0,0; 13,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 24,23</t>
+          <t>0,0; 15,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,89</t>
+          <t>1,62; 9,65</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 15,0</t>
+          <t>3,03; 16,05</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,87</t>
+          <t>4,47; 11,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,76</t>
+          <t>1,67; 7,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,5</t>
+          <t>2,51; 9,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,4</t>
+          <t>1,48; 6,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,93</t>
+          <t>3,11; 9,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,52</t>
+          <t>2,27; 8,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,43</t>
+          <t>0,55; 4,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,33</t>
+          <t>0,53; 4,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,3</t>
+          <t>4,42; 9,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,3</t>
+          <t>2,62; 6,28</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,62</t>
+          <t>1,74; 5,68</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,36</t>
+          <t>1,4; 4,55</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1226</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1693</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>498</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>765</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>947</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>533; 4600</t>
+          <t>0; 4601</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2253</t>
+          <t>0; 5595</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3719</t>
+          <t>584; 6178</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>520; 4276</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4782</t>
+          <t>0; 2269</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>615; 5709</t>
+          <t>0; 3791</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3416</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>575; 5944</t>
+          <t>807; 5642</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6221</t>
+          <t>0; 5452</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>823; 7397</t>
+          <t>833; 6801</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3805</t>
+          <t>0; 3490</t>
         </is>
       </c>
     </row>
@@ -2281,32 +2281,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2349,32 +2349,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1508</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3437</t>
+          <t>0; 4926</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4614</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4616</t>
+          <t>0; 3668</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>637; 5620</t>
+          <t>641; 5570</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5866</t>
+          <t>0; 4860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,34 +2557,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1401</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>645</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4260</t>
+          <t>0; 3153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4583</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3159</t>
+          <t>0; 4287</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3915</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3666</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>617; 5417</t>
+          <t>647; 5397</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3512</t>
+          <t>0; 3871</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4792</t>
+          <t>0; 3225</t>
         </is>
       </c>
     </row>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2765,32 +2765,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>443</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2769</t>
+          <t>0; 3652</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2337</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3987</t>
+          <t>0; 2714</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2347</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4341</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2361</t>
+          <t>0; 2701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>675</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2998,29 +2998,29 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>675</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>841</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4222</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2770</t>
+          <t>0; 3463</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3543</t>
+          <t>0; 3106</t>
         </is>
       </c>
     </row>
@@ -3113,27 +3113,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -3181,32 +3181,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1197</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1936</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>747</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1197</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>613; 5120</t>
+          <t>0; 3608</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3348</t>
+          <t>0; 3722</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3615</t>
+          <t>605; 4702</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3653</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1223; 6498</t>
+          <t>1200; 6933</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 4482</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,49 +3389,49 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>4146</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4047</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3501</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>6109</t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5327</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1370; 6926</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1436; 7637</t>
+          <t>622; 4723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3309</t>
+          <t>0; 3814</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>411; 5039</t>
+          <t>1132; 7721</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1370; 6984</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>616; 4826</t>
+          <t>1420; 7866</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3661</t>
+          <t>0; 3085</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1287; 9071</t>
+          <t>392; 5878</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1373; 7656</t>
+          <t>1338; 7087</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2787; 10759</t>
+          <t>2755; 10340</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>575; 5207</t>
+          <t>598; 5109</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2817; 12157</t>
+          <t>2370; 10244</t>
         </is>
       </c>
     </row>
@@ -3529,37 +3529,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,37 +3597,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>1064</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>910</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2669</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>598; 5120</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3243</t>
+          <t>699; 5995</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>602; 5383</t>
+          <t>0; 3442</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>726; 6061</t>
+          <t>0; 3192</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1074; 6504</t>
+          <t>1068; 6346</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1349; 6888</t>
+          <t>1390; 7374</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4042; 12371</t>
+          <t>6438; 16150</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3480; 11430</t>
+          <t>2640; 11462</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>693; 5733</t>
+          <t>3098; 11480</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>818; 7824</t>
+          <t>2440; 10178</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6322; 17167</t>
+          <t>3898; 12252</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2916; 11872</t>
+          <t>3342; 11801</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3205; 11629</t>
+          <t>706; 5554</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2987; 11528</t>
+          <t>763; 6885</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11788; 25026</t>
+          <t>11887; 25235</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7275; 19237</t>
+          <t>8004; 19176</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4736; 14087</t>
+          <t>4362; 14236</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4735; 15681</t>
+          <t>4306; 14012</t>
         </is>
       </c>
     </row>
